--- a/Viajante/Volume_por_rota.xlsx
+++ b/Viajante/Volume_por_rota.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="43">
   <si>
     <t>COD FLUXO</t>
   </si>
@@ -76,7 +76,7 @@
     <t>% MDRs APURADOS</t>
   </si>
   <si>
-    <t>FCA/FPT</t>
+    <t>FCA</t>
   </si>
   <si>
     <t>Apr</t>
@@ -115,22 +115,22 @@
     <t>Sep</t>
   </si>
   <si>
-    <t>800005741</t>
-  </si>
-  <si>
-    <t>HBA</t>
-  </si>
-  <si>
-    <t>CARRETA SIDER</t>
-  </si>
-  <si>
-    <t>MONTAGEM-MG</t>
+    <t>800002588</t>
+  </si>
+  <si>
+    <t>DANA II</t>
+  </si>
+  <si>
+    <t>TRUCK SIDER</t>
+  </si>
+  <si>
+    <t>FPT</t>
   </si>
   <si>
     <t>FTL</t>
   </si>
   <si>
-    <t>FURLONG</t>
+    <t>CARGOLIFT</t>
   </si>
   <si>
     <t>VOLUME</t>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>Manter coleta</t>
+  </si>
+  <si>
+    <t>Cortar coleta do último veículo</t>
   </si>
 </sst>
 </file>
@@ -564,10 +567,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B2">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -597,25 +600,25 @@
         <v>39</v>
       </c>
       <c r="L2">
-        <v>907.1</v>
+        <v>388.2</v>
       </c>
       <c r="M2">
-        <v>113064.2</v>
+        <v>62925.3</v>
       </c>
       <c r="N2">
-        <v>3568</v>
+        <v>1038</v>
       </c>
       <c r="O2">
-        <v>1138.85</v>
+        <v>1838.64</v>
       </c>
       <c r="P2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q2">
-        <v>75.59999999999999</v>
+        <v>20.4</v>
       </c>
       <c r="R2">
-        <v>94.90000000000001</v>
+        <v>96.77</v>
       </c>
       <c r="S2" t="s">
         <v>40</v>
@@ -626,10 +629,10 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B3">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -659,28 +662,28 @@
         <v>39</v>
       </c>
       <c r="L3">
-        <v>1391.6</v>
+        <v>595.6</v>
       </c>
       <c r="M3">
-        <v>173609.4</v>
+        <v>97941.60000000001</v>
       </c>
       <c r="N3">
-        <v>5514</v>
+        <v>1538</v>
       </c>
       <c r="O3">
-        <v>1748.1</v>
+        <v>2897.09</v>
       </c>
       <c r="P3">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="Q3">
-        <v>77.3</v>
+        <v>20.5</v>
       </c>
       <c r="R3">
-        <v>97.12</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="S3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T3">
         <v>100</v>
@@ -688,10 +691,10 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B4">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -721,25 +724,25 @@
         <v>39</v>
       </c>
       <c r="L4">
-        <v>835.9</v>
+        <v>327.2</v>
       </c>
       <c r="M4">
-        <v>104905.7</v>
+        <v>58500.4</v>
       </c>
       <c r="N4">
-        <v>3320</v>
+        <v>969</v>
       </c>
       <c r="O4">
-        <v>1049.73</v>
+        <v>1829.62</v>
       </c>
       <c r="P4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Q4">
-        <v>76</v>
+        <v>17.2</v>
       </c>
       <c r="R4">
-        <v>95.43000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="S4" t="s">
         <v>40</v>
@@ -750,10 +753,10 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B5">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -783,28 +786,28 @@
         <v>39</v>
       </c>
       <c r="L5">
-        <v>730.3</v>
+        <v>329.3</v>
       </c>
       <c r="M5">
-        <v>90179.3</v>
+        <v>53080.4</v>
       </c>
       <c r="N5">
-        <v>2954</v>
+        <v>895</v>
       </c>
       <c r="O5">
-        <v>917.29</v>
+        <v>1551.56</v>
       </c>
       <c r="P5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q5">
-        <v>73</v>
+        <v>20.6</v>
       </c>
       <c r="R5">
-        <v>91.73</v>
+        <v>96.97</v>
       </c>
       <c r="S5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T5">
         <v>100</v>
@@ -812,10 +815,10 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B6">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
@@ -845,28 +848,28 @@
         <v>39</v>
       </c>
       <c r="L6">
-        <v>1049</v>
+        <v>343.4</v>
       </c>
       <c r="M6">
-        <v>128321.8</v>
+        <v>64262.7</v>
       </c>
       <c r="N6">
-        <v>3947</v>
+        <v>1038</v>
       </c>
       <c r="O6">
-        <v>1315.19</v>
+        <v>1900.09</v>
       </c>
       <c r="P6">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q6">
-        <v>74.90000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="R6">
-        <v>93.94</v>
+        <v>95</v>
       </c>
       <c r="S6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T6">
         <v>100</v>
@@ -874,10 +877,10 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B7">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
@@ -907,25 +910,25 @@
         <v>39</v>
       </c>
       <c r="L7">
-        <v>1008.1</v>
+        <v>431.7</v>
       </c>
       <c r="M7">
-        <v>124068.3</v>
+        <v>70392.2</v>
       </c>
       <c r="N7">
-        <v>3893</v>
+        <v>1163</v>
       </c>
       <c r="O7">
-        <v>1264.89</v>
+        <v>1976.29</v>
       </c>
       <c r="P7">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q7">
-        <v>77.5</v>
+        <v>21.6</v>
       </c>
       <c r="R7">
-        <v>97.3</v>
+        <v>98.81</v>
       </c>
       <c r="S7" t="s">
         <v>41</v>
@@ -936,10 +939,10 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B8">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
@@ -969,28 +972,28 @@
         <v>39</v>
       </c>
       <c r="L8">
-        <v>934.1</v>
+        <v>424.8</v>
       </c>
       <c r="M8">
-        <v>118062.2</v>
+        <v>68401.3</v>
       </c>
       <c r="N8">
-        <v>3748</v>
+        <v>1114</v>
       </c>
       <c r="O8">
-        <v>1173.89</v>
+        <v>2017.7</v>
       </c>
       <c r="P8">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Q8">
-        <v>77.8</v>
+        <v>20.2</v>
       </c>
       <c r="R8">
-        <v>97.81999999999999</v>
+        <v>96.08</v>
       </c>
       <c r="S8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -998,10 +1001,10 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B9">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
@@ -1031,28 +1034,28 @@
         <v>39</v>
       </c>
       <c r="L9">
-        <v>1262.2</v>
+        <v>537.8</v>
       </c>
       <c r="M9">
-        <v>157918.9</v>
+        <v>87485.89999999999</v>
       </c>
       <c r="N9">
-        <v>5064</v>
+        <v>1387</v>
       </c>
       <c r="O9">
-        <v>1586.26</v>
+        <v>2600.42</v>
       </c>
       <c r="P9">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="Q9">
-        <v>78.90000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="R9">
-        <v>99.14</v>
+        <v>96.31</v>
       </c>
       <c r="S9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -1060,10 +1063,10 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B10">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -1093,25 +1096,25 @@
         <v>39</v>
       </c>
       <c r="L10">
-        <v>1377.2</v>
+        <v>575.4</v>
       </c>
       <c r="M10">
-        <v>169549.5</v>
+        <v>94453.39999999999</v>
       </c>
       <c r="N10">
-        <v>5409</v>
+        <v>1522</v>
       </c>
       <c r="O10">
-        <v>1729.7</v>
+        <v>2710.83</v>
       </c>
       <c r="P10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="Q10">
-        <v>76.5</v>
+        <v>20.6</v>
       </c>
       <c r="R10">
-        <v>96.09</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="S10" t="s">
         <v>40</v>
@@ -1122,10 +1125,10 @@
     </row>
     <row r="11" spans="1:20">
       <c r="A11">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B11">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -1155,25 +1158,25 @@
         <v>39</v>
       </c>
       <c r="L11">
-        <v>1377.2</v>
+        <v>481.5</v>
       </c>
       <c r="M11">
-        <v>169356.2</v>
+        <v>86982.39999999999</v>
       </c>
       <c r="N11">
-        <v>5117</v>
+        <v>1384</v>
       </c>
       <c r="O11">
-        <v>1726.57</v>
+        <v>2505.26</v>
       </c>
       <c r="P11">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Q11">
-        <v>76.5</v>
+        <v>18.5</v>
       </c>
       <c r="R11">
-        <v>95.92</v>
+        <v>96.36</v>
       </c>
       <c r="S11" t="s">
         <v>40</v>
@@ -1184,10 +1187,10 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B12">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -1217,25 +1220,25 @@
         <v>39</v>
       </c>
       <c r="L12">
-        <v>1164.3</v>
+        <v>420.9</v>
       </c>
       <c r="M12">
-        <v>144421.8</v>
+        <v>74015.3</v>
       </c>
       <c r="N12">
-        <v>4474</v>
+        <v>1161</v>
       </c>
       <c r="O12">
-        <v>1460.79</v>
+        <v>2198.22</v>
       </c>
       <c r="P12">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q12">
-        <v>77.59999999999999</v>
+        <v>19.1</v>
       </c>
       <c r="R12">
-        <v>97.39</v>
+        <v>99.92</v>
       </c>
       <c r="S12" t="s">
         <v>41</v>
@@ -1246,10 +1249,10 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B13">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
@@ -1279,28 +1282,28 @@
         <v>39</v>
       </c>
       <c r="L13">
-        <v>1154.2</v>
+        <v>416</v>
       </c>
       <c r="M13">
-        <v>143514.6</v>
+        <v>70646.2</v>
       </c>
       <c r="N13">
-        <v>4433</v>
+        <v>948</v>
       </c>
       <c r="O13">
-        <v>1448.49</v>
+        <v>2184.22</v>
       </c>
       <c r="P13">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q13">
-        <v>76.90000000000001</v>
+        <v>18.9</v>
       </c>
       <c r="R13">
-        <v>96.56999999999999</v>
+        <v>99.28</v>
       </c>
       <c r="S13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T13">
         <v>100</v>

--- a/Viajante/Volume_por_rota.xlsx
+++ b/Viajante/Volume_por_rota.xlsx
@@ -121,7 +121,7 @@
     <t>DANA II</t>
   </si>
   <si>
-    <t>TRUCK SIDER</t>
+    <t>CARRETA SIDER</t>
   </si>
   <si>
     <t>FPT</t>
@@ -609,16 +609,16 @@
         <v>1038</v>
       </c>
       <c r="O2">
-        <v>1838.64</v>
+        <v>1131.46</v>
       </c>
       <c r="P2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q2">
-        <v>20.4</v>
+        <v>32.4</v>
       </c>
       <c r="R2">
-        <v>96.77</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="S2" t="s">
         <v>40</v>
@@ -671,16 +671,16 @@
         <v>1538</v>
       </c>
       <c r="O3">
-        <v>2897.09</v>
+        <v>1782.82</v>
       </c>
       <c r="P3">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Q3">
-        <v>20.5</v>
+        <v>33.1</v>
       </c>
       <c r="R3">
-        <v>99.90000000000001</v>
+        <v>99.05</v>
       </c>
       <c r="S3" t="s">
         <v>41</v>
@@ -733,16 +733,16 @@
         <v>969</v>
       </c>
       <c r="O4">
-        <v>1829.62</v>
+        <v>1125.92</v>
       </c>
       <c r="P4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q4">
-        <v>17.2</v>
+        <v>27.3</v>
       </c>
       <c r="R4">
-        <v>96.3</v>
+        <v>93.83</v>
       </c>
       <c r="S4" t="s">
         <v>40</v>
@@ -795,16 +795,16 @@
         <v>895</v>
       </c>
       <c r="O5">
-        <v>1551.56</v>
+        <v>954.79</v>
       </c>
       <c r="P5">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>20.6</v>
+        <v>32.9</v>
       </c>
       <c r="R5">
-        <v>96.97</v>
+        <v>95.48</v>
       </c>
       <c r="S5" t="s">
         <v>41</v>
@@ -857,19 +857,19 @@
         <v>1038</v>
       </c>
       <c r="O6">
-        <v>1900.09</v>
+        <v>1169.3</v>
       </c>
       <c r="P6">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Q6">
-        <v>17.2</v>
+        <v>28.6</v>
       </c>
       <c r="R6">
-        <v>95</v>
+        <v>97.44</v>
       </c>
       <c r="S6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T6">
         <v>100</v>
@@ -919,19 +919,19 @@
         <v>1163</v>
       </c>
       <c r="O7">
-        <v>1976.29</v>
+        <v>1216.18</v>
       </c>
       <c r="P7">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="Q7">
-        <v>21.6</v>
+        <v>33.2</v>
       </c>
       <c r="R7">
-        <v>98.81</v>
+        <v>93.55</v>
       </c>
       <c r="S7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T7">
         <v>100</v>
@@ -981,16 +981,16 @@
         <v>1114</v>
       </c>
       <c r="O8">
-        <v>2017.7</v>
+        <v>1241.69</v>
       </c>
       <c r="P8">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Q8">
-        <v>20.2</v>
+        <v>32.7</v>
       </c>
       <c r="R8">
-        <v>96.08</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="S8" t="s">
         <v>40</v>
@@ -1043,16 +1043,16 @@
         <v>1387</v>
       </c>
       <c r="O9">
-        <v>2600.42</v>
+        <v>1600.26</v>
       </c>
       <c r="P9">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="Q9">
-        <v>19.9</v>
+        <v>31.6</v>
       </c>
       <c r="R9">
-        <v>96.31</v>
+        <v>94.13</v>
       </c>
       <c r="S9" t="s">
         <v>42</v>
@@ -1105,19 +1105,19 @@
         <v>1522</v>
       </c>
       <c r="O10">
-        <v>2710.83</v>
+        <v>1668.21</v>
       </c>
       <c r="P10">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Q10">
-        <v>20.6</v>
+        <v>33.8</v>
       </c>
       <c r="R10">
-        <v>96.81999999999999</v>
+        <v>98.13</v>
       </c>
       <c r="S10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -1167,13 +1167,13 @@
         <v>1384</v>
       </c>
       <c r="O11">
-        <v>2505.26</v>
+        <v>1541.71</v>
       </c>
       <c r="P11">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="Q11">
-        <v>18.5</v>
+        <v>30.1</v>
       </c>
       <c r="R11">
         <v>96.36</v>
@@ -1229,16 +1229,16 @@
         <v>1161</v>
       </c>
       <c r="O12">
-        <v>2198.22</v>
+        <v>1352.76</v>
       </c>
       <c r="P12">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Q12">
-        <v>19.1</v>
+        <v>30.1</v>
       </c>
       <c r="R12">
-        <v>99.92</v>
+        <v>96.63</v>
       </c>
       <c r="S12" t="s">
         <v>41</v>
@@ -1291,19 +1291,19 @@
         <v>948</v>
       </c>
       <c r="O13">
-        <v>2184.22</v>
+        <v>1344.13</v>
       </c>
       <c r="P13">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Q13">
-        <v>18.9</v>
+        <v>29.7</v>
       </c>
       <c r="R13">
-        <v>99.28</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="S13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T13">
         <v>100</v>

--- a/Viajante/Volume_por_rota.xlsx
+++ b/Viajante/Volume_por_rota.xlsx
@@ -115,22 +115,22 @@
     <t>Sep</t>
   </si>
   <si>
-    <t>800002588</t>
-  </si>
-  <si>
-    <t>DANA II</t>
+    <t>800006503</t>
+  </si>
+  <si>
+    <t>COOPER STANDARD III</t>
   </si>
   <si>
     <t>CARRETA SIDER</t>
   </si>
   <si>
-    <t>FPT</t>
+    <t>MONTAGEM-MG</t>
   </si>
   <si>
     <t>FTL</t>
   </si>
   <si>
-    <t>CARGOLIFT</t>
+    <t>FURLONG</t>
   </si>
   <si>
     <t>VOLUME</t>
@@ -567,10 +567,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="B2">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -629,10 +629,10 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -691,10 +691,10 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="B4">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="B5">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -815,10 +815,10 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
@@ -939,10 +939,10 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="B9">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="B10">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="11" spans="1:20">
       <c r="A11">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="B12">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -1249,10 +1249,10 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="B13">
-        <v>1128</v>
+        <v>1080</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>

--- a/Viajante/Volume_por_rota.xlsx
+++ b/Viajante/Volume_por_rota.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="42">
   <si>
     <t>COD FLUXO</t>
   </si>
@@ -140,9 +140,6 @@
   </si>
   <si>
     <t>Manter coleta</t>
-  </si>
-  <si>
-    <t>Cortar coleta do último veículo</t>
   </si>
 </sst>
 </file>
@@ -600,25 +597,25 @@
         <v>39</v>
       </c>
       <c r="L2">
-        <v>388.2</v>
+        <v>503.8</v>
       </c>
       <c r="M2">
-        <v>62925.3</v>
+        <v>47721.8</v>
       </c>
       <c r="N2">
-        <v>1038</v>
+        <v>649</v>
       </c>
       <c r="O2">
-        <v>1131.46</v>
+        <v>636.1799999999999</v>
       </c>
       <c r="P2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q2">
-        <v>32.4</v>
+        <v>72</v>
       </c>
       <c r="R2">
-        <v>94.29000000000001</v>
+        <v>90.88</v>
       </c>
       <c r="S2" t="s">
         <v>40</v>
@@ -662,28 +659,28 @@
         <v>39</v>
       </c>
       <c r="L3">
-        <v>595.6</v>
+        <v>818.7</v>
       </c>
       <c r="M3">
-        <v>97941.60000000001</v>
+        <v>77544.39999999999</v>
       </c>
       <c r="N3">
-        <v>1538</v>
+        <v>1051</v>
       </c>
       <c r="O3">
-        <v>1782.82</v>
+        <v>1032.78</v>
       </c>
       <c r="P3">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q3">
-        <v>33.1</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="R3">
-        <v>99.05</v>
+        <v>93.89</v>
       </c>
       <c r="S3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T3">
         <v>100</v>
@@ -724,28 +721,28 @@
         <v>39</v>
       </c>
       <c r="L4">
-        <v>327.2</v>
+        <v>526.8</v>
       </c>
       <c r="M4">
-        <v>58500.4</v>
+        <v>49510.2</v>
       </c>
       <c r="N4">
-        <v>969</v>
+        <v>678</v>
       </c>
       <c r="O4">
-        <v>1125.92</v>
+        <v>664.9400000000001</v>
       </c>
       <c r="P4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>27.3</v>
+        <v>75.3</v>
       </c>
       <c r="R4">
-        <v>93.83</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="S4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T4">
         <v>100</v>
@@ -786,28 +783,28 @@
         <v>39</v>
       </c>
       <c r="L5">
-        <v>329.3</v>
+        <v>418.6</v>
       </c>
       <c r="M5">
-        <v>53080.4</v>
+        <v>39559.5</v>
       </c>
       <c r="N5">
-        <v>895</v>
+        <v>537</v>
       </c>
       <c r="O5">
-        <v>954.79</v>
+        <v>528.03</v>
       </c>
       <c r="P5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>32.9</v>
+        <v>69.8</v>
       </c>
       <c r="R5">
-        <v>95.48</v>
+        <v>88</v>
       </c>
       <c r="S5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T5">
         <v>100</v>
@@ -848,25 +845,25 @@
         <v>39</v>
       </c>
       <c r="L6">
-        <v>343.4</v>
+        <v>621.7</v>
       </c>
       <c r="M6">
-        <v>64262.7</v>
+        <v>58893.9</v>
       </c>
       <c r="N6">
-        <v>1038</v>
+        <v>800</v>
       </c>
       <c r="O6">
-        <v>1169.3</v>
+        <v>784.74</v>
       </c>
       <c r="P6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>28.6</v>
+        <v>77.7</v>
       </c>
       <c r="R6">
-        <v>97.44</v>
+        <v>98.09</v>
       </c>
       <c r="S6" t="s">
         <v>41</v>
@@ -910,25 +907,25 @@
         <v>39</v>
       </c>
       <c r="L7">
-        <v>431.7</v>
+        <v>570.7</v>
       </c>
       <c r="M7">
-        <v>70392.2</v>
+        <v>54442.7</v>
       </c>
       <c r="N7">
-        <v>1163</v>
+        <v>736</v>
       </c>
       <c r="O7">
-        <v>1216.18</v>
+        <v>720.67</v>
       </c>
       <c r="P7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>33.2</v>
+        <v>71.3</v>
       </c>
       <c r="R7">
-        <v>93.55</v>
+        <v>90.08</v>
       </c>
       <c r="S7" t="s">
         <v>40</v>
@@ -972,28 +969,28 @@
         <v>39</v>
       </c>
       <c r="L8">
-        <v>424.8</v>
+        <v>527</v>
       </c>
       <c r="M8">
-        <v>68401.3</v>
+        <v>49724.4</v>
       </c>
       <c r="N8">
-        <v>1114</v>
+        <v>680</v>
       </c>
       <c r="O8">
-        <v>1241.69</v>
+        <v>665.78</v>
       </c>
       <c r="P8">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>32.7</v>
+        <v>75.3</v>
       </c>
       <c r="R8">
-        <v>95.51000000000001</v>
+        <v>95.11</v>
       </c>
       <c r="S8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -1034,28 +1031,28 @@
         <v>39</v>
       </c>
       <c r="L9">
-        <v>537.8</v>
+        <v>719.9</v>
       </c>
       <c r="M9">
-        <v>87485.89999999999</v>
+        <v>68327.7</v>
       </c>
       <c r="N9">
-        <v>1387</v>
+        <v>928</v>
       </c>
       <c r="O9">
-        <v>1600.26</v>
+        <v>909.42</v>
       </c>
       <c r="P9">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>31.6</v>
+        <v>72</v>
       </c>
       <c r="R9">
-        <v>94.13</v>
+        <v>90.94</v>
       </c>
       <c r="S9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -1096,28 +1093,28 @@
         <v>39</v>
       </c>
       <c r="L10">
-        <v>575.4</v>
+        <v>736.6</v>
       </c>
       <c r="M10">
-        <v>94453.39999999999</v>
+        <v>70150.3</v>
       </c>
       <c r="N10">
-        <v>1522</v>
+        <v>950</v>
       </c>
       <c r="O10">
-        <v>1668.21</v>
+        <v>930.28</v>
       </c>
       <c r="P10">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>33.8</v>
+        <v>73.7</v>
       </c>
       <c r="R10">
-        <v>98.13</v>
+        <v>93.03</v>
       </c>
       <c r="S10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -1158,25 +1155,25 @@
         <v>39</v>
       </c>
       <c r="L11">
-        <v>481.5</v>
+        <v>747.2</v>
       </c>
       <c r="M11">
-        <v>86982.39999999999</v>
+        <v>71169.7</v>
       </c>
       <c r="N11">
-        <v>1384</v>
+        <v>961</v>
       </c>
       <c r="O11">
-        <v>1541.71</v>
+        <v>942.74</v>
       </c>
       <c r="P11">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>30.1</v>
+        <v>74.7</v>
       </c>
       <c r="R11">
-        <v>96.36</v>
+        <v>94.27</v>
       </c>
       <c r="S11" t="s">
         <v>40</v>
@@ -1220,28 +1217,28 @@
         <v>39</v>
       </c>
       <c r="L12">
-        <v>420.9</v>
+        <v>637.1</v>
       </c>
       <c r="M12">
-        <v>74015.3</v>
+        <v>60577.4</v>
       </c>
       <c r="N12">
-        <v>1161</v>
+        <v>823</v>
       </c>
       <c r="O12">
-        <v>1352.76</v>
+        <v>805.1900000000001</v>
       </c>
       <c r="P12">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>30.1</v>
+        <v>70.8</v>
       </c>
       <c r="R12">
-        <v>96.63</v>
+        <v>89.47</v>
       </c>
       <c r="S12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -1282,28 +1279,28 @@
         <v>39</v>
       </c>
       <c r="L13">
-        <v>416</v>
+        <v>612.2</v>
       </c>
       <c r="M13">
-        <v>70646.2</v>
+        <v>57665.5</v>
       </c>
       <c r="N13">
-        <v>948</v>
+        <v>791</v>
       </c>
       <c r="O13">
-        <v>1344.13</v>
+        <v>773.72</v>
       </c>
       <c r="P13">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>29.7</v>
+        <v>76.5</v>
       </c>
       <c r="R13">
-        <v>96.01000000000001</v>
+        <v>96.72</v>
       </c>
       <c r="S13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T13">
         <v>100</v>

--- a/Viajante/Volume_por_rota.xlsx
+++ b/Viajante/Volume_por_rota.xlsx
@@ -13,10 +13,149 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="42">
+  <si>
+    <t>COD FLUXO</t>
+  </si>
+  <si>
+    <t>COD DESTINO</t>
+  </si>
+  <si>
+    <t>DESTINO</t>
+  </si>
+  <si>
+    <t>Mês</t>
+  </si>
+  <si>
+    <t>CÓDIGOS FORNECEDORES</t>
+  </si>
+  <si>
+    <t>FORNECEDORES NA ROTA</t>
+  </si>
+  <si>
+    <t>VEÍCULO</t>
+  </si>
+  <si>
+    <t>TECNOLOGIA</t>
+  </si>
+  <si>
+    <t>MOT</t>
+  </si>
+  <si>
+    <t>TRANSPORTADORA</t>
+  </si>
+  <si>
+    <t>TIPO DE SATURAÇÃO</t>
+  </si>
+  <si>
+    <t>VOLUME TOTAL (m³)</t>
+  </si>
+  <si>
+    <t>PESO TOTAL (kg)</t>
+  </si>
+  <si>
+    <t>EMBALAGENS TOTAL</t>
+  </si>
+  <si>
+    <t>SATURAÇÃO TOTAL (%)</t>
+  </si>
+  <si>
+    <t>CARGAS</t>
+  </si>
+  <si>
+    <t>CAP. ÚTIL (m³)</t>
+  </si>
+  <si>
+    <t>CAP. ÚTIL (%)</t>
+  </si>
+  <si>
+    <t>SUGESTÃO</t>
+  </si>
+  <si>
+    <t>% MDRs APURADOS</t>
+  </si>
+  <si>
+    <t>FCA</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>800006503</t>
+  </si>
+  <si>
+    <t>COOPER STANDARD III</t>
+  </si>
+  <si>
+    <t>CARRETA SIDER</t>
+  </si>
+  <si>
+    <t>MONTAGEM-MG</t>
+  </si>
+  <si>
+    <t>FTL</t>
+  </si>
+  <si>
+    <t>FURLONG</t>
+  </si>
+  <si>
+    <t>VOLUME</t>
+  </si>
+  <si>
+    <t>Alterar último veículo para menor porte</t>
+  </si>
+  <si>
+    <t>Manter coleta</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -32,7 +171,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -40,12 +179,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -340,9 +497,816 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2">
+        <v>22</v>
+      </c>
+      <c r="B2">
+        <v>1080</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2">
+        <v>503.8</v>
+      </c>
+      <c r="M2">
+        <v>47721.8</v>
+      </c>
+      <c r="N2">
+        <v>649</v>
+      </c>
+      <c r="O2">
+        <v>636.1799999999999</v>
+      </c>
+      <c r="P2">
+        <v>7</v>
+      </c>
+      <c r="Q2">
+        <v>72</v>
+      </c>
+      <c r="R2">
+        <v>90.88</v>
+      </c>
+      <c r="S2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3">
+        <v>22</v>
+      </c>
+      <c r="B3">
+        <v>1080</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3">
+        <v>818.7</v>
+      </c>
+      <c r="M3">
+        <v>77544.39999999999</v>
+      </c>
+      <c r="N3">
+        <v>1051</v>
+      </c>
+      <c r="O3">
+        <v>1032.78</v>
+      </c>
+      <c r="P3">
+        <v>11</v>
+      </c>
+      <c r="Q3">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="R3">
+        <v>93.89</v>
+      </c>
+      <c r="S3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4">
+        <v>22</v>
+      </c>
+      <c r="B4">
+        <v>1080</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4">
+        <v>526.8</v>
+      </c>
+      <c r="M4">
+        <v>49510.2</v>
+      </c>
+      <c r="N4">
+        <v>678</v>
+      </c>
+      <c r="O4">
+        <v>664.9400000000001</v>
+      </c>
+      <c r="P4">
+        <v>7</v>
+      </c>
+      <c r="Q4">
+        <v>75.3</v>
+      </c>
+      <c r="R4">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="S4" t="s">
+        <v>41</v>
+      </c>
+      <c r="T4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5">
+        <v>22</v>
+      </c>
+      <c r="B5">
+        <v>1080</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5">
+        <v>418.6</v>
+      </c>
+      <c r="M5">
+        <v>39559.5</v>
+      </c>
+      <c r="N5">
+        <v>537</v>
+      </c>
+      <c r="O5">
+        <v>528.03</v>
+      </c>
+      <c r="P5">
+        <v>6</v>
+      </c>
+      <c r="Q5">
+        <v>69.8</v>
+      </c>
+      <c r="R5">
+        <v>88</v>
+      </c>
+      <c r="S5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6">
+        <v>22</v>
+      </c>
+      <c r="B6">
+        <v>1080</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6">
+        <v>621.7</v>
+      </c>
+      <c r="M6">
+        <v>58893.9</v>
+      </c>
+      <c r="N6">
+        <v>800</v>
+      </c>
+      <c r="O6">
+        <v>784.74</v>
+      </c>
+      <c r="P6">
+        <v>8</v>
+      </c>
+      <c r="Q6">
+        <v>77.7</v>
+      </c>
+      <c r="R6">
+        <v>98.09</v>
+      </c>
+      <c r="S6" t="s">
+        <v>41</v>
+      </c>
+      <c r="T6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7">
+        <v>22</v>
+      </c>
+      <c r="B7">
+        <v>1080</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7">
+        <v>570.7</v>
+      </c>
+      <c r="M7">
+        <v>54442.7</v>
+      </c>
+      <c r="N7">
+        <v>736</v>
+      </c>
+      <c r="O7">
+        <v>720.67</v>
+      </c>
+      <c r="P7">
+        <v>8</v>
+      </c>
+      <c r="Q7">
+        <v>71.3</v>
+      </c>
+      <c r="R7">
+        <v>90.08</v>
+      </c>
+      <c r="S7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>1080</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8">
+        <v>527</v>
+      </c>
+      <c r="M8">
+        <v>49724.4</v>
+      </c>
+      <c r="N8">
+        <v>680</v>
+      </c>
+      <c r="O8">
+        <v>665.78</v>
+      </c>
+      <c r="P8">
+        <v>7</v>
+      </c>
+      <c r="Q8">
+        <v>75.3</v>
+      </c>
+      <c r="R8">
+        <v>95.11</v>
+      </c>
+      <c r="S8" t="s">
+        <v>41</v>
+      </c>
+      <c r="T8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9">
+        <v>22</v>
+      </c>
+      <c r="B9">
+        <v>1080</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9">
+        <v>719.9</v>
+      </c>
+      <c r="M9">
+        <v>68327.7</v>
+      </c>
+      <c r="N9">
+        <v>928</v>
+      </c>
+      <c r="O9">
+        <v>909.42</v>
+      </c>
+      <c r="P9">
+        <v>10</v>
+      </c>
+      <c r="Q9">
+        <v>72</v>
+      </c>
+      <c r="R9">
+        <v>90.94</v>
+      </c>
+      <c r="S9" t="s">
+        <v>40</v>
+      </c>
+      <c r="T9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10">
+        <v>22</v>
+      </c>
+      <c r="B10">
+        <v>1080</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10">
+        <v>736.6</v>
+      </c>
+      <c r="M10">
+        <v>70150.3</v>
+      </c>
+      <c r="N10">
+        <v>950</v>
+      </c>
+      <c r="O10">
+        <v>930.28</v>
+      </c>
+      <c r="P10">
+        <v>10</v>
+      </c>
+      <c r="Q10">
+        <v>73.7</v>
+      </c>
+      <c r="R10">
+        <v>93.03</v>
+      </c>
+      <c r="S10" t="s">
+        <v>40</v>
+      </c>
+      <c r="T10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11">
+        <v>22</v>
+      </c>
+      <c r="B11">
+        <v>1080</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11">
+        <v>747.2</v>
+      </c>
+      <c r="M11">
+        <v>71169.7</v>
+      </c>
+      <c r="N11">
+        <v>961</v>
+      </c>
+      <c r="O11">
+        <v>942.74</v>
+      </c>
+      <c r="P11">
+        <v>10</v>
+      </c>
+      <c r="Q11">
+        <v>74.7</v>
+      </c>
+      <c r="R11">
+        <v>94.27</v>
+      </c>
+      <c r="S11" t="s">
+        <v>40</v>
+      </c>
+      <c r="T11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12">
+        <v>22</v>
+      </c>
+      <c r="B12">
+        <v>1080</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" t="s">
+        <v>38</v>
+      </c>
+      <c r="K12" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12">
+        <v>637.1</v>
+      </c>
+      <c r="M12">
+        <v>60577.4</v>
+      </c>
+      <c r="N12">
+        <v>823</v>
+      </c>
+      <c r="O12">
+        <v>805.1900000000001</v>
+      </c>
+      <c r="P12">
+        <v>9</v>
+      </c>
+      <c r="Q12">
+        <v>70.8</v>
+      </c>
+      <c r="R12">
+        <v>89.47</v>
+      </c>
+      <c r="S12" t="s">
+        <v>40</v>
+      </c>
+      <c r="T12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>1080</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K13" t="s">
+        <v>39</v>
+      </c>
+      <c r="L13">
+        <v>612.2</v>
+      </c>
+      <c r="M13">
+        <v>57665.5</v>
+      </c>
+      <c r="N13">
+        <v>791</v>
+      </c>
+      <c r="O13">
+        <v>773.72</v>
+      </c>
+      <c r="P13">
+        <v>8</v>
+      </c>
+      <c r="Q13">
+        <v>76.5</v>
+      </c>
+      <c r="R13">
+        <v>96.72</v>
+      </c>
+      <c r="S13" t="s">
+        <v>41</v>
+      </c>
+      <c r="T13">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Viajante/Volume_por_rota.xlsx
+++ b/Viajante/Volume_por_rota.xlsx
@@ -76,7 +76,7 @@
     <t>% MDRs APURADOS</t>
   </si>
   <si>
-    <t>FCA</t>
+    <t>FPT</t>
   </si>
   <si>
     <t>Apr</t>
@@ -115,25 +115,25 @@
     <t>Sep</t>
   </si>
   <si>
-    <t>800006503</t>
-  </si>
-  <si>
-    <t>COOPER STANDARD III</t>
+    <t>800033128</t>
+  </si>
+  <si>
+    <t>MAHLE</t>
   </si>
   <si>
     <t>CARRETA SIDER</t>
   </si>
   <si>
-    <t>MONTAGEM-MG</t>
+    <t>MONTAGEM-SP</t>
   </si>
   <si>
     <t>FTL</t>
   </si>
   <si>
-    <t>FURLONG</t>
-  </si>
-  <si>
-    <t>VOLUME</t>
+    <t>JSL</t>
+  </si>
+  <si>
+    <t>PESO</t>
   </si>
   <si>
     <t>Alterar último veículo para menor porte</t>
@@ -564,7 +564,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="B2">
         <v>1080</v>
@@ -597,25 +597,25 @@
         <v>39</v>
       </c>
       <c r="L2">
-        <v>503.8</v>
+        <v>61349.1</v>
       </c>
       <c r="M2">
-        <v>47721.8</v>
+        <v>5735796.7</v>
       </c>
       <c r="N2">
-        <v>649</v>
+        <v>24278</v>
       </c>
       <c r="O2">
-        <v>636.1799999999999</v>
+        <v>22943.16</v>
       </c>
       <c r="P2">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="Q2">
-        <v>72</v>
+        <v>266.7</v>
       </c>
       <c r="R2">
-        <v>90.88</v>
+        <v>99.75</v>
       </c>
       <c r="S2" t="s">
         <v>40</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="B3">
         <v>1080</v>
@@ -659,28 +659,28 @@
         <v>39</v>
       </c>
       <c r="L3">
-        <v>818.7</v>
+        <v>97221.10000000001</v>
       </c>
       <c r="M3">
-        <v>77544.39999999999</v>
+        <v>9165920.699999999</v>
       </c>
       <c r="N3">
-        <v>1051</v>
+        <v>38460</v>
       </c>
       <c r="O3">
-        <v>1032.78</v>
+        <v>36663.71</v>
       </c>
       <c r="P3">
-        <v>11</v>
+        <v>367</v>
       </c>
       <c r="Q3">
-        <v>74.40000000000001</v>
+        <v>264.9</v>
       </c>
       <c r="R3">
-        <v>93.89</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="S3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T3">
         <v>100</v>
@@ -688,7 +688,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="B4">
         <v>1080</v>
@@ -721,25 +721,25 @@
         <v>39</v>
       </c>
       <c r="L4">
-        <v>526.8</v>
+        <v>46822</v>
       </c>
       <c r="M4">
-        <v>49510.2</v>
+        <v>4673839.4</v>
       </c>
       <c r="N4">
-        <v>678</v>
+        <v>20163</v>
       </c>
       <c r="O4">
-        <v>664.9400000000001</v>
+        <v>18695.35</v>
       </c>
       <c r="P4">
-        <v>7</v>
+        <v>187</v>
       </c>
       <c r="Q4">
-        <v>75.3</v>
+        <v>250.4</v>
       </c>
       <c r="R4">
-        <v>94.98999999999999</v>
+        <v>99.98</v>
       </c>
       <c r="S4" t="s">
         <v>41</v>
@@ -750,7 +750,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="B5">
         <v>1080</v>
@@ -783,25 +783,25 @@
         <v>39</v>
       </c>
       <c r="L5">
-        <v>418.6</v>
+        <v>51311.8</v>
       </c>
       <c r="M5">
-        <v>39559.5</v>
+        <v>4807560</v>
       </c>
       <c r="N5">
-        <v>537</v>
+        <v>19774</v>
       </c>
       <c r="O5">
-        <v>528.03</v>
+        <v>19230.23</v>
       </c>
       <c r="P5">
-        <v>6</v>
+        <v>193</v>
       </c>
       <c r="Q5">
-        <v>69.8</v>
+        <v>265.9</v>
       </c>
       <c r="R5">
-        <v>88</v>
+        <v>99.64</v>
       </c>
       <c r="S5" t="s">
         <v>40</v>
@@ -812,7 +812,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="B6">
         <v>1080</v>
@@ -845,25 +845,25 @@
         <v>39</v>
       </c>
       <c r="L6">
-        <v>621.7</v>
+        <v>53063.5</v>
       </c>
       <c r="M6">
-        <v>58893.9</v>
+        <v>5417696.2</v>
       </c>
       <c r="N6">
-        <v>800</v>
+        <v>22889</v>
       </c>
       <c r="O6">
-        <v>784.74</v>
+        <v>21670.81</v>
       </c>
       <c r="P6">
-        <v>8</v>
+        <v>217</v>
       </c>
       <c r="Q6">
-        <v>77.7</v>
+        <v>244.5</v>
       </c>
       <c r="R6">
-        <v>98.09</v>
+        <v>99.87</v>
       </c>
       <c r="S6" t="s">
         <v>41</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="B7">
         <v>1080</v>
@@ -907,28 +907,28 @@
         <v>39</v>
       </c>
       <c r="L7">
-        <v>570.7</v>
+        <v>71434.10000000001</v>
       </c>
       <c r="M7">
-        <v>54442.7</v>
+        <v>6690972</v>
       </c>
       <c r="N7">
-        <v>736</v>
+        <v>27704</v>
       </c>
       <c r="O7">
-        <v>720.67</v>
+        <v>26763.87</v>
       </c>
       <c r="P7">
-        <v>8</v>
+        <v>268</v>
       </c>
       <c r="Q7">
-        <v>71.3</v>
+        <v>266.5</v>
       </c>
       <c r="R7">
-        <v>90.08</v>
+        <v>99.87</v>
       </c>
       <c r="S7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T7">
         <v>100</v>
@@ -936,7 +936,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="B8">
         <v>1080</v>
@@ -969,28 +969,28 @@
         <v>39</v>
       </c>
       <c r="L8">
-        <v>527</v>
+        <v>66432.2</v>
       </c>
       <c r="M8">
-        <v>49724.4</v>
+        <v>6186255.5</v>
       </c>
       <c r="N8">
-        <v>680</v>
+        <v>25888</v>
       </c>
       <c r="O8">
-        <v>665.78</v>
+        <v>24745.01</v>
       </c>
       <c r="P8">
-        <v>7</v>
+        <v>248</v>
       </c>
       <c r="Q8">
-        <v>75.3</v>
+        <v>267.9</v>
       </c>
       <c r="R8">
-        <v>95.11</v>
+        <v>99.78</v>
       </c>
       <c r="S8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -998,7 +998,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="B9">
         <v>1080</v>
@@ -1031,28 +1031,28 @@
         <v>39</v>
       </c>
       <c r="L9">
-        <v>719.9</v>
+        <v>88054.7</v>
       </c>
       <c r="M9">
-        <v>68327.7</v>
+        <v>8240045.1</v>
       </c>
       <c r="N9">
-        <v>928</v>
+        <v>34563</v>
       </c>
       <c r="O9">
-        <v>909.42</v>
+        <v>32960.2</v>
       </c>
       <c r="P9">
-        <v>10</v>
+        <v>330</v>
       </c>
       <c r="Q9">
-        <v>72</v>
+        <v>266.8</v>
       </c>
       <c r="R9">
-        <v>90.94</v>
+        <v>99.88</v>
       </c>
       <c r="S9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="B10">
         <v>1080</v>
@@ -1093,25 +1093,25 @@
         <v>39</v>
       </c>
       <c r="L10">
-        <v>736.6</v>
+        <v>93571.3</v>
       </c>
       <c r="M10">
-        <v>70150.3</v>
+        <v>8777739.4</v>
       </c>
       <c r="N10">
-        <v>950</v>
+        <v>36388</v>
       </c>
       <c r="O10">
-        <v>930.28</v>
+        <v>35110.95</v>
       </c>
       <c r="P10">
-        <v>10</v>
+        <v>352</v>
       </c>
       <c r="Q10">
-        <v>73.7</v>
+        <v>265.8</v>
       </c>
       <c r="R10">
-        <v>93.03</v>
+        <v>99.75</v>
       </c>
       <c r="S10" t="s">
         <v>40</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="11" spans="1:20">
       <c r="A11">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="B11">
         <v>1080</v>
@@ -1155,25 +1155,25 @@
         <v>39</v>
       </c>
       <c r="L11">
-        <v>747.2</v>
+        <v>66899.2</v>
       </c>
       <c r="M11">
-        <v>71169.7</v>
+        <v>6678461</v>
       </c>
       <c r="N11">
-        <v>961</v>
+        <v>28996</v>
       </c>
       <c r="O11">
-        <v>942.74</v>
+        <v>26713.85</v>
       </c>
       <c r="P11">
-        <v>10</v>
+        <v>268</v>
       </c>
       <c r="Q11">
-        <v>74.7</v>
+        <v>249.6</v>
       </c>
       <c r="R11">
-        <v>94.27</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="S11" t="s">
         <v>40</v>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="B12">
         <v>1080</v>
@@ -1217,28 +1217,28 @@
         <v>39</v>
       </c>
       <c r="L12">
-        <v>637.1</v>
+        <v>63200.7</v>
       </c>
       <c r="M12">
-        <v>60577.4</v>
+        <v>6195728.9</v>
       </c>
       <c r="N12">
-        <v>823</v>
+        <v>26406</v>
       </c>
       <c r="O12">
-        <v>805.1900000000001</v>
+        <v>24782.88</v>
       </c>
       <c r="P12">
-        <v>9</v>
+        <v>248</v>
       </c>
       <c r="Q12">
-        <v>70.8</v>
+        <v>254.8</v>
       </c>
       <c r="R12">
-        <v>89.47</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="S12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="B13">
         <v>1080</v>
@@ -1279,28 +1279,28 @@
         <v>39</v>
       </c>
       <c r="L13">
-        <v>612.2</v>
+        <v>67708.2</v>
       </c>
       <c r="M13">
-        <v>57665.5</v>
+        <v>6506613.6</v>
       </c>
       <c r="N13">
-        <v>791</v>
+        <v>27301</v>
       </c>
       <c r="O13">
-        <v>773.72</v>
+        <v>26026.47</v>
       </c>
       <c r="P13">
-        <v>8</v>
+        <v>261</v>
       </c>
       <c r="Q13">
-        <v>76.5</v>
+        <v>259.4</v>
       </c>
       <c r="R13">
-        <v>96.72</v>
+        <v>99.72</v>
       </c>
       <c r="S13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T13">
         <v>100</v>
